--- a/haleon/haleon-판매데이터-더미.xlsx
+++ b/haleon/haleon-판매데이터-더미.xlsx
@@ -516,7 +516,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>자세한 절차는 학습사이트 → 교시별 학습자료 → 1교시 Excel 을 보세요.</t>
+          <t>자세한 절차는 학습사이트 상단 메뉴 [1교시] 를 보세요.</t>
         </is>
       </c>
     </row>
